--- a/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval_by_type.xlsx
@@ -587,19 +587,19 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -609,25 +609,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3636</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="8">
@@ -668,19 +668,19 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0.6667</v>
@@ -696,22 +696,22 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
